--- a/4_NLU/DL_Lecture/Evaluation result_Homework4.xlsx
+++ b/4_NLU/DL_Lecture/Evaluation result_Homework4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\김강민\가톨릭대학교\수업\2024-1\딥러닝\Homework4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kokyungwoo\PycharmProjects\DeepLearningStudy\4_NLU\DL_Lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634B28BE-A021-4E1A-9B4E-E4107664DB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9412945E-0913-47E1-9923-1096F291386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -95,9 +95,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> [결과 정리]</t>
-  </si>
-  <si>
     <t>Convolutional Neural Network for Multi-class Text Classification-Evaluation Report</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -115,6 +112,27 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNN-Rand</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNN-static</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNN-multi-channel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> [결과 정리]
+cnn-static 은 파인튜닝을 할 수 없고 임베딩을 고정하면 적응령이 가장 떨어짐 -&gt; 표현이 다채로운 태스크는 단어 의미를 조정이 중요함을 시사
+cnn-non-static 은 파인튜닝이 가능해 static보다 높은 정확도를 보이지만 rand보단 낮음 
+cnn-rand 는 가장 높은 성능을 사전 파인튜닝없이 가장 높은 성능을 보였음 , 데이터 규모가 커서 학습을 빠르게 수렴했을 가능성이 있고, non-static의 초기 지점이 잘못되었을 가능성이 있음
+cnn-multi-channel 은 두 채널을 섞었지만 랜덤에는 미치지 못했고 두 채널의 공유로 성능이 조금 올라갔지만 rand 보다 낮음 , 여전히 초기지점의 영향이 있엇을 수 있을듯함 
+필터 수등 파라미터를 조절한다면 multi-channel이 충분히 Rand를 앞설 수 있을 듯함 , 이론상 multi channel 의 val/acc 이 98정도 되었지만 정확도가 95로 낮게 나온거로 봐서는 과적합됫을 가능성이 높음</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -193,7 +211,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -440,17 +458,6 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -479,7 +486,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -489,9 +496,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -537,36 +541,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -603,11 +577,35 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,6 +690,627 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>737155</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>180758</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>432127</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>107673</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF61BCD1-43F9-D70F-58B8-81A2CEE1F8EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10502351" y="3410975"/>
+          <a:ext cx="4374646" cy="1740807"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>993426</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>134447</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>466960</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>149087</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0BAAC28-AB65-9A34-2D0F-3F2250483F08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10758622" y="5385621"/>
+          <a:ext cx="4153208" cy="1671162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>643412</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>44951</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1456543</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7F57248-9C0A-BE3D-B022-DCB492BF0B2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="643412" y="3275168"/>
+          <a:ext cx="5128370" cy="2042267"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>81822</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1349849</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>16566</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC4FF035-A5DC-1717-FE14-8D5F90320455}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="736148" y="5428644"/>
+          <a:ext cx="4928940" cy="1909748"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>455055</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>157370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>579724</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66260</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD671C2D-A56E-0AD1-86A2-45F8651168F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14899925" y="3387587"/>
+          <a:ext cx="4456473" cy="1722782"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>469672</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>215713</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24A799CA-FAE2-B956-A814-C86172FC1642}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14914542" y="5158119"/>
+          <a:ext cx="4732171" cy="1807555"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>596348</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1813891</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>289891</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="직사각형 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D559913B-BE65-AAB7-1CBD-5D6DC04BB0D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1250674" y="2849217"/>
+          <a:ext cx="1217543" cy="273326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>CNN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t> - non-static</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>583096</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>342899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>790161</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>218660</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="직사각형 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95205F70-426A-4A6A-8113-81BD3ABFFB8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11996531" y="2777986"/>
+          <a:ext cx="1217543" cy="273326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>CNN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t> - static</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>727214</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>354495</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>975691</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>230256</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="직사각형 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{573DAA1B-AADA-4E61-B27F-3C3190CD275A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7875105" y="2789582"/>
+          <a:ext cx="1217543" cy="273326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>CNN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t> - rand</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>511865</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>395907</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1896717</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>271668</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="직사각형 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB5B3D98-E3BC-4FB7-931C-EA58ABDB63C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16050039" y="2830994"/>
+          <a:ext cx="1384852" cy="273326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
+            <a:t>CNN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" baseline="0"/>
+            <a:t> - multi-channel</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1441174</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>41413</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>679155</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>157369</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D38BCDD4-2D06-B534-D316-447416185B15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5756413" y="3271630"/>
+          <a:ext cx="4687938" cy="1929848"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1548848</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>190501</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>737152</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57557</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7726ED25-D509-AFDC-2355-3F8369B37170}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5864087" y="5234610"/>
+          <a:ext cx="4638261" cy="1937708"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -991,68 +1610,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:Q18"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:Q36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.58203125" customWidth="1"/>
-    <col min="2" max="2" width="31.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.58203125" customWidth="1"/>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
     <col min="4" max="4" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.875" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="7" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.58203125" customWidth="1"/>
+    <col min="7" max="7" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.625" customWidth="1"/>
     <col min="9" max="9" width="13.25" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="13.25" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.58203125" customWidth="1"/>
-    <col min="15" max="1025" width="8.58203125" customWidth="1"/>
+    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="15" max="1025" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:17" ht="30.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="37" t="s">
+    <row r="1" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:17" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+    </row>
+    <row r="3" spans="2:17" ht="24.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="30"/>
+      <c r="C3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-    </row>
-    <row r="3" spans="2:17" ht="23.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="41"/>
-      <c r="C3" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="40"/>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B4" s="42"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="29"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="31"/>
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1065,7 +1684,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>4</v>
@@ -1086,247 +1705,314 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="32">
+        <v>0.94569999999999999</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>100</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>0.5</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1E-4</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1E-3</v>
+      </c>
+      <c r="M5" s="7">
+        <v>300</v>
+      </c>
+      <c r="N5" s="9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="8">
+      <c r="C6" s="32">
+        <v>0.95569999999999999</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="7">
+        <v>100</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="7">
         <v>1E-4</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="8">
+      <c r="K6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="7">
         <v>1E-3</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M6" s="7">
         <v>300</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N6" s="9">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="14" t="s">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="32">
+        <v>0.94430000000000003</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7">
+        <v>100</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1E-4</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1E-3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>300</v>
+      </c>
+      <c r="N7" s="9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="32">
+        <v>0.95430000000000004</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="7">
+        <v>100</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1E-4</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1E-3</v>
+      </c>
+      <c r="M8" s="7">
+        <v>300</v>
+      </c>
+      <c r="N8" s="9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="6"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="21"/>
-    </row>
-    <row r="9" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="22"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="24"/>
-    </row>
-    <row r="10" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="22"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="24"/>
-    </row>
-    <row r="11" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="24"/>
-    </row>
-    <row r="12" spans="2:17" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="27"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B13" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.45">
-      <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-    </row>
-    <row r="18" spans="2:17" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="36"/>
+    </row>
+    <row r="12" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="36"/>
+    </row>
+    <row r="13" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="34"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="36"/>
+    </row>
+    <row r="14" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="36"/>
+    </row>
+    <row r="15" spans="2:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="34"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="36"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B17" s="34"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="34"/>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -1340,20 +2026,302 @@
       <c r="L18" s="35"/>
       <c r="M18" s="35"/>
       <c r="N18" s="36"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="36"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="36"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="34"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="36"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="36"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="36"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B27" s="34"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="36"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="36"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="34"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="36"/>
+    </row>
+    <row r="30" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="37"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="39"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B31" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="19"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="22"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="22"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="22"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="22"/>
+    </row>
+    <row r="36" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="23"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B8:N12"/>
-    <mergeCell ref="B13:N18"/>
+    <mergeCell ref="B31:N36"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="D3:N3"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B11:N30"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>